--- a/ig/improve-doc/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/improve-doc/CodeSystem-terminologie-nabm.xlsx
@@ -31,7 +31,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/#terminologie-nabm</t>
+    <t>OID:1.2.250.1.215.300.2</t>
   </si>
   <si>
     <t>Version</t>
